--- a/artfynd/A 15386-2023 artfynd.xlsx
+++ b/artfynd/A 15386-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>113679753</v>
       </c>
       <c r="B2" t="n">
-        <v>79263</v>
+        <v>79265</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>113681118</v>
       </c>
       <c r="B3" t="n">
-        <v>90148</v>
+        <v>90150</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 15386-2023 artfynd.xlsx
+++ b/artfynd/A 15386-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113679753</v>
+        <v>113681118</v>
       </c>
       <c r="B2" t="n">
-        <v>79265</v>
+        <v>90151</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>5442</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>687816</v>
+        <v>687781</v>
       </c>
       <c r="R2" t="n">
-        <v>7015735</v>
+        <v>7015683</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -762,12 +762,12 @@
       <c r="AG2" t="b">
         <v>0</v>
       </c>
-      <c r="AS2" t="inlineStr">
-        <is>
-          <t>Tomas Rask</t>
-        </is>
-      </c>
       <c r="AT2" t="inlineStr"/>
+      <c r="AU2" t="inlineStr">
+        <is>
+          <t>Kristofer Wester</t>
+        </is>
+      </c>
       <c r="AW2" t="inlineStr">
         <is>
           <t>Helene Andersson</t>
@@ -775,7 +775,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Helene Andersson, Tomas Rask</t>
+          <t>Helene Andersson, Kristofer Wester</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113681118</v>
+        <v>113679753</v>
       </c>
       <c r="B3" t="n">
-        <v>90150</v>
+        <v>79265</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,21 +802,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5442</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -826,10 +826,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>687781</v>
+        <v>687816</v>
       </c>
       <c r="R3" t="n">
-        <v>7015683</v>
+        <v>7015735</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -873,12 +873,12 @@
       <c r="AG3" t="b">
         <v>0</v>
       </c>
+      <c r="AS3" t="inlineStr">
+        <is>
+          <t>Tomas Rask</t>
+        </is>
+      </c>
       <c r="AT3" t="inlineStr"/>
-      <c r="AU3" t="inlineStr">
-        <is>
-          <t>Kristofer Wester</t>
-        </is>
-      </c>
       <c r="AW3" t="inlineStr">
         <is>
           <t>Helene Andersson</t>
@@ -886,7 +886,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Helene Andersson, Kristofer Wester</t>
+          <t>Helene Andersson, Tomas Rask</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">

--- a/artfynd/A 15386-2023 artfynd.xlsx
+++ b/artfynd/A 15386-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113681118</v>
+        <v>113679753</v>
       </c>
       <c r="B2" t="n">
-        <v>90151</v>
+        <v>79265</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5442</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>687781</v>
+        <v>687816</v>
       </c>
       <c r="R2" t="n">
-        <v>7015683</v>
+        <v>7015735</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -762,12 +762,12 @@
       <c r="AG2" t="b">
         <v>0</v>
       </c>
+      <c r="AS2" t="inlineStr">
+        <is>
+          <t>Tomas Rask</t>
+        </is>
+      </c>
       <c r="AT2" t="inlineStr"/>
-      <c r="AU2" t="inlineStr">
-        <is>
-          <t>Kristofer Wester</t>
-        </is>
-      </c>
       <c r="AW2" t="inlineStr">
         <is>
           <t>Helene Andersson</t>
@@ -775,7 +775,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Helene Andersson, Kristofer Wester</t>
+          <t>Helene Andersson, Tomas Rask</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113679753</v>
+        <v>113681118</v>
       </c>
       <c r="B3" t="n">
-        <v>79265</v>
+        <v>90155</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,21 +802,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>5442</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -826,10 +826,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>687816</v>
+        <v>687781</v>
       </c>
       <c r="R3" t="n">
-        <v>7015735</v>
+        <v>7015683</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -873,12 +873,12 @@
       <c r="AG3" t="b">
         <v>0</v>
       </c>
-      <c r="AS3" t="inlineStr">
-        <is>
-          <t>Tomas Rask</t>
-        </is>
-      </c>
       <c r="AT3" t="inlineStr"/>
+      <c r="AU3" t="inlineStr">
+        <is>
+          <t>Kristofer Wester</t>
+        </is>
+      </c>
       <c r="AW3" t="inlineStr">
         <is>
           <t>Helene Andersson</t>
@@ -886,7 +886,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Helene Andersson, Tomas Rask</t>
+          <t>Helene Andersson, Kristofer Wester</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">

--- a/artfynd/A 15386-2023 artfynd.xlsx
+++ b/artfynd/A 15386-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113679753</v>
+        <v>113681118</v>
       </c>
       <c r="B2" t="n">
-        <v>79265</v>
+        <v>90155</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>5442</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>687816</v>
+        <v>687781</v>
       </c>
       <c r="R2" t="n">
-        <v>7015735</v>
+        <v>7015683</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -762,12 +762,12 @@
       <c r="AG2" t="b">
         <v>0</v>
       </c>
-      <c r="AS2" t="inlineStr">
-        <is>
-          <t>Tomas Rask</t>
-        </is>
-      </c>
       <c r="AT2" t="inlineStr"/>
+      <c r="AU2" t="inlineStr">
+        <is>
+          <t>Kristofer Wester</t>
+        </is>
+      </c>
       <c r="AW2" t="inlineStr">
         <is>
           <t>Helene Andersson</t>
@@ -775,7 +775,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Helene Andersson, Tomas Rask</t>
+          <t>Helene Andersson, Kristofer Wester</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113681118</v>
+        <v>113679753</v>
       </c>
       <c r="B3" t="n">
-        <v>90155</v>
+        <v>79265</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,21 +802,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5442</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -826,10 +826,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>687781</v>
+        <v>687816</v>
       </c>
       <c r="R3" t="n">
-        <v>7015683</v>
+        <v>7015735</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -873,12 +873,12 @@
       <c r="AG3" t="b">
         <v>0</v>
       </c>
+      <c r="AS3" t="inlineStr">
+        <is>
+          <t>Tomas Rask</t>
+        </is>
+      </c>
       <c r="AT3" t="inlineStr"/>
-      <c r="AU3" t="inlineStr">
-        <is>
-          <t>Kristofer Wester</t>
-        </is>
-      </c>
       <c r="AW3" t="inlineStr">
         <is>
           <t>Helene Andersson</t>
@@ -886,7 +886,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Helene Andersson, Kristofer Wester</t>
+          <t>Helene Andersson, Tomas Rask</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">

--- a/artfynd/A 15386-2023 artfynd.xlsx
+++ b/artfynd/A 15386-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113681118</v>
+        <v>113679753</v>
       </c>
       <c r="B2" t="n">
-        <v>90155</v>
+        <v>79265</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5442</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>687781</v>
+        <v>687816</v>
       </c>
       <c r="R2" t="n">
-        <v>7015683</v>
+        <v>7015735</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -762,12 +762,12 @@
       <c r="AG2" t="b">
         <v>0</v>
       </c>
+      <c r="AS2" t="inlineStr">
+        <is>
+          <t>Tomas Rask</t>
+        </is>
+      </c>
       <c r="AT2" t="inlineStr"/>
-      <c r="AU2" t="inlineStr">
-        <is>
-          <t>Kristofer Wester</t>
-        </is>
-      </c>
       <c r="AW2" t="inlineStr">
         <is>
           <t>Helene Andersson</t>
@@ -775,7 +775,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Helene Andersson, Kristofer Wester</t>
+          <t>Helene Andersson, Tomas Rask</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113679753</v>
+        <v>113681118</v>
       </c>
       <c r="B3" t="n">
-        <v>79265</v>
+        <v>90155</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,21 +802,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>5442</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -826,10 +826,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>687816</v>
+        <v>687781</v>
       </c>
       <c r="R3" t="n">
-        <v>7015735</v>
+        <v>7015683</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -873,12 +873,12 @@
       <c r="AG3" t="b">
         <v>0</v>
       </c>
-      <c r="AS3" t="inlineStr">
-        <is>
-          <t>Tomas Rask</t>
-        </is>
-      </c>
       <c r="AT3" t="inlineStr"/>
+      <c r="AU3" t="inlineStr">
+        <is>
+          <t>Kristofer Wester</t>
+        </is>
+      </c>
       <c r="AW3" t="inlineStr">
         <is>
           <t>Helene Andersson</t>
@@ -886,7 +886,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Helene Andersson, Tomas Rask</t>
+          <t>Helene Andersson, Kristofer Wester</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">

--- a/artfynd/A 15386-2023 artfynd.xlsx
+++ b/artfynd/A 15386-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 15386-2023 artfynd.xlsx
+++ b/artfynd/A 15386-2023 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>113681118</v>
       </c>
       <c r="B2" t="n">
-        <v>90352</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -709,6 +704,9 @@
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Buhalsberget, Ång</t>
@@ -759,6 +757,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -775,12 +774,12 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Helene Andersson, Kristofer Wester</t>
+          <t>Kristofer Wester</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Naturvärdesinventering </t>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
     </row>
@@ -789,12 +788,7 @@
         <v>113679753</v>
       </c>
       <c r="B3" t="n">
-        <v>79558</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80415</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -886,12 +880,12 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Helene Andersson, Tomas Rask</t>
+          <t>Tomas Rask</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Naturvärdesinventering </t>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
     </row>

--- a/artfynd/A 15386-2023 artfynd.xlsx
+++ b/artfynd/A 15386-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>113681118</v>
       </c>
       <c r="B2" t="n">
-        <v>91910</v>
+        <v>91913</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         <v>113679753</v>
       </c>
       <c r="B3" t="n">
-        <v>80420</v>
+        <v>80422</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 15386-2023 artfynd.xlsx
+++ b/artfynd/A 15386-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>113681118</v>
       </c>
       <c r="B2" t="n">
-        <v>91913</v>
+        <v>91919</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         <v>113679753</v>
       </c>
       <c r="B3" t="n">
-        <v>80422</v>
+        <v>80424</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 15386-2023 artfynd.xlsx
+++ b/artfynd/A 15386-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>113681118</v>
       </c>
       <c r="B2" t="n">
-        <v>91919</v>
+        <v>91929</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         <v>113679753</v>
       </c>
       <c r="B3" t="n">
-        <v>80424</v>
+        <v>80432</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 15386-2023 artfynd.xlsx
+++ b/artfynd/A 15386-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>113681118</v>
       </c>
       <c r="B2" t="n">
-        <v>91929</v>
+        <v>91930</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 15386-2023 artfynd.xlsx
+++ b/artfynd/A 15386-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -782,6 +787,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113681118</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -888,8 +898,17 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113679753</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>